--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487075_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487075_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.098000000000001</v>
+        <v>6.7001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3679</v>
+        <v>3.2999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7301</v>
+        <v>3.4002</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5203</v>
+        <v>4.8007</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9227</v>
+        <v>4.0582</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5976</v>
+        <v>0.7426</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9483</v>
+        <v>4.3868</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5239</v>
+        <v>4.3054</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4245</v>
+        <v>0.0814</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.428</v>
+        <v>0.4139</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6012</v>
+        <v>-0.2473</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8268</v>
+        <v>0.6612</v>
       </c>
       <c r="P2" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5441</v>
+        <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9058</v>
+        <v>1.7486</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2918</v>
+        <v>0.8854</v>
       </c>
       <c r="U2" t="n">
-        <v>0.614</v>
+        <v>0.8632</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2859</v>
+        <v>-0.0422</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2859</v>
+        <v>-0.0422</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8294</v>
+        <v>5.6133</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0009</v>
+        <v>5.1242</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8285</v>
+        <v>0.4891</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8007</v>
+        <v>3.5203</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0582</v>
+        <v>2.9227</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7426</v>
+        <v>0.5976</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3868</v>
+        <v>4.9483</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3054</v>
+        <v>3.5239</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0814</v>
+        <v>1.4245</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4139</v>
+        <v>-1.428</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2473</v>
+        <v>-0.6012</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6612</v>
+        <v>-0.8268</v>
       </c>
       <c r="P3" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8779</v>
+        <v>1.4211</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5864</v>
+        <v>1.048</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2915</v>
+        <v>0.3731</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0422</v>
+        <v>0.2859</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0422</v>
+        <v>0.2859</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2227</v>
+        <v>4.5305</v>
       </c>
       <c r="E4" t="n">
-        <v>1.503</v>
+        <v>2.8643</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7197</v>
+        <v>1.6662</v>
       </c>
       <c r="G4" t="n">
         <v>1.9364</v>
@@ -766,13 +766,13 @@
         <v>2.5091</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0648</v>
+        <v>1.243</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0708</v>
+        <v>0.2905</v>
       </c>
       <c r="U4" t="n">
-        <v>1.006</v>
+        <v>0.9525</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2842</v>
+        <v>2.9445</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8256</v>
+        <v>-0.1653</v>
       </c>
       <c r="F5" t="n">
         <v>3.1098</v>
@@ -844,10 +844,10 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3702</v>
+        <v>0.2902</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7139</v>
+        <v>-0.0535</v>
       </c>
       <c r="U5" t="n">
         <v>0.3437</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1482</v>
+        <v>2.6033</v>
       </c>
       <c r="E6" t="n">
         <v>-1.2712</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4194</v>
+        <v>3.8745</v>
       </c>
       <c r="G6" t="n">
         <v>3.7354</v>
@@ -922,13 +922,13 @@
         <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.306</v>
+        <v>0.149</v>
       </c>
       <c r="T6" t="n">
         <v>0.0727</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3788</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.831</v>
+        <v>2.0848</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5571</v>
+        <v>-0.3568</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3881</v>
+        <v>2.4416</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3137</v>
@@ -1000,13 +1000,13 @@
         <v>2.5091</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2678</v>
+        <v>1.5216</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6214</v>
+        <v>0.8216</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6464</v>
+        <v>0.7</v>
       </c>
       <c r="V7" t="n">
         <v>2.4559</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3739</v>
+        <v>1.7606</v>
       </c>
       <c r="E8" t="n">
-        <v>0.219</v>
+        <v>0.8199</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1549</v>
+        <v>0.9407</v>
       </c>
       <c r="G8" t="n">
         <v>0.1398</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.111</v>
+        <v>0.4977</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5949</v>
+        <v>0.006</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7059</v>
+        <v>0.4918</v>
       </c>
       <c r="V8" t="n">
         <v>-0.614</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2991</v>
+        <v>0.0351</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.537</v>
+        <v>-2.3368</v>
       </c>
       <c r="F9" t="n">
-        <v>2.238</v>
+        <v>2.3718</v>
       </c>
       <c r="G9" t="n">
         <v>1.2589</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7859</v>
+        <v>-0.4518</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3569</v>
+        <v>-0.1566</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.429</v>
+        <v>-0.2952</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>D. PÉREZ DE SAN ROMÁN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3023</v>
+        <v>-0.2055</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0664</v>
+        <v>-0.1973</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3687</v>
+        <v>-0.0083</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5967</v>
+        <v>0.9019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9956</v>
+        <v>0.5941</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5923</v>
+        <v>0.3077</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2389</v>
+        <v>0.0407</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4113</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1724</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8356</v>
+        <v>0.8612</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4157</v>
+        <v>0.5941</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4199</v>
+        <v>0.267</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0.193</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5646</v>
+        <v>-0.4006</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7998</v>
+        <v>-0.238</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7647</v>
+        <v>-0.1626</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2702</v>
+        <v>-0.8999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. PÉREZ DE SAN ROMÁN</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3126</v>
+        <v>-0.4828</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1973</v>
+        <v>-0.0337</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1154</v>
+        <v>-0.449</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9019</v>
+        <v>-0.5967</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5941</v>
+        <v>0.9956</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3077</v>
+        <v>-1.5923</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0407</v>
+        <v>1.2389</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2.4113</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0407</v>
+        <v>-1.1724</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8612</v>
+        <v>-1.8356</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5941</v>
+        <v>-1.4157</v>
       </c>
       <c r="O11" t="n">
-        <v>0.267</v>
+        <v>-0.4199</v>
       </c>
       <c r="P11" t="n">
-        <v>0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5076000000000001</v>
+        <v>1.3841</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.238</v>
+        <v>0.6997</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2697</v>
+        <v>0.6844</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8999</v>
+        <v>-1.2702</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8999</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.903</v>
+        <v>-0.8435</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7263</v>
+        <v>-1.6668</v>
       </c>
       <c r="F12" t="n">
         <v>0.8232</v>
@@ -1390,10 +1390,10 @@
         <v>0.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9201</v>
+        <v>-0.8606</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5354</v>
+        <v>-0.4759</v>
       </c>
       <c r="U12" t="n">
         <v>-0.3847</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2336</v>
+        <v>-1.7061</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1655</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0681</v>
+        <v>-1.8004</v>
       </c>
       <c r="G13" t="n">
         <v>0.3122</v>
@@ -1468,13 +1468,13 @@
         <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.4376</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0132</v>
+        <v>0.273</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1031</v>
+        <v>0.1646</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.73680000000001</v>
+        <v>23.0343</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8772</v>
+        <v>6.174699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>16.8595</v>
+        <v>16.8594</v>
       </c>
       <c r="G14" t="n">
         <v>16.6875</v>
@@ -1516,10 +1516,10 @@
         <v>13.9207</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7668</v>
+        <v>2.766799999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>17.4522</v>
+        <v>17.45219999999999</v>
       </c>
       <c r="K14" t="n">
         <v>15.1923</v>
@@ -1534,7 +1534,7 @@
         <v>-1.2717</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5068000000000005</v>
+        <v>0.5068000000000003</v>
       </c>
       <c r="P14" t="n">
         <v>0.9652000000000001</v>
@@ -1543,16 +1543,16 @@
         <v>-18.3356</v>
       </c>
       <c r="R14" t="n">
-        <v>19.30080000000001</v>
+        <v>19.3008</v>
       </c>
       <c r="S14" t="n">
-        <v>6.682600000000001</v>
+        <v>6.9799</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8754</v>
+        <v>3.1729</v>
       </c>
       <c r="U14" t="n">
-        <v>3.8069</v>
+        <v>3.8071</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5983</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.766</v>
+        <v>1.7531</v>
       </c>
       <c r="E15" t="n">
-        <v>3.332</v>
+        <v>3.1318</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.566</v>
+        <v>-1.3786</v>
       </c>
       <c r="G15" t="n">
         <v>3.1894</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5236</v>
+        <v>-1.5365</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3437</v>
+        <v>-0.544</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1799</v>
+        <v>-0.9925</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2859</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0814</v>
+        <v>-0.4455</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6904</v>
+        <v>-0.5511</v>
       </c>
       <c r="F16" t="n">
-        <v>0.609</v>
+        <v>0.1057</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.107</v>
+        <v>0.8679</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8682</v>
+        <v>-1.1592</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2388</v>
+        <v>2.0271</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1046</v>
+        <v>1.3281</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1085</v>
+        <v>-0.5848</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2131</v>
+        <v>1.9129</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0024</v>
+        <v>-0.4601</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9767</v>
+        <v>-0.5743</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0257</v>
+        <v>0.1142</v>
       </c>
       <c r="P16" t="n">
+        <v>-1.3511</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.579</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.965</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.5441</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.0516</v>
+        <v>-0.2482</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4627</v>
+        <v>-0.235</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4111</v>
+        <v>-0.0132</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4982</v>
+        <v>0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>1.842</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7459</v>
+        <v>-0.8309</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8515</v>
+        <v>-0.6904</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1057</v>
+        <v>-0.1405</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8679</v>
+        <v>-3.107</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1592</v>
+        <v>-1.8682</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0271</v>
+        <v>-1.2388</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3281</v>
+        <v>-1.1046</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5848</v>
+        <v>0.1085</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9129</v>
+        <v>-1.2131</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4601</v>
+        <v>-2.0024</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5743</v>
+        <v>-1.9767</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1142</v>
+        <v>-0.0257</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5486</v>
+        <v>-0.8011</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5354</v>
+        <v>-0.4627</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0132</v>
+        <v>-0.3385</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2859</v>
+        <v>2.4982</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2859</v>
+        <v>1.842</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.466</v>
+        <v>-1.2832</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3261</v>
+        <v>-1.5211</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7921</v>
+        <v>0.2379</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6416</v>
+        <v>-3.8537</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6634</v>
+        <v>-2.8069</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9782</v>
+        <v>-1.0468</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6597</v>
+        <v>-2.5055</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1142</v>
+        <v>-1.8786</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>-0.6269</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.982</v>
+        <v>-1.3481</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5493</v>
+        <v>-0.9283</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4327</v>
+        <v>-0.4199</v>
       </c>
       <c r="P18" t="n">
-        <v>0.772</v>
+        <v>1.9301</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7317</v>
+        <v>-0.3017</v>
       </c>
       <c r="T18" t="n">
-        <v>1.051</v>
+        <v>-0.2435</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3193</v>
+        <v>-0.0582</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3281</v>
+        <v>0.9421</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8999</v>
+        <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>L. BARNES HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4904</v>
+        <v>-2.037</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6212</v>
+        <v>-2.181</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1308</v>
+        <v>0.144</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8537</v>
+        <v>-1.0977</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8069</v>
+        <v>-1.7346</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0468</v>
+        <v>0.6369</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5055</v>
+        <v>0.2306</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8786</v>
+        <v>0.1085</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6269</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3481</v>
+        <v>-1.3283</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9283</v>
+        <v>-1.8431</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4199</v>
+        <v>0.5148</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5089</v>
+        <v>-1.1323</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3437</v>
+        <v>-0.4815</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1653</v>
+        <v>-0.6508</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BARNES HERNANDEZ</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.271</v>
+        <v>-2.1799</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2811</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0101</v>
+        <v>-1.6047</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0977</v>
+        <v>-2.6416</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7346</v>
+        <v>-1.6634</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6369</v>
+        <v>-0.9782</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2306</v>
+        <v>-0.6597</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1085</v>
+        <v>-0.1142</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1221</v>
+        <v>-0.5455</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3283</v>
+        <v>-1.982</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8431</v>
+        <v>-1.5493</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5148</v>
+        <v>-0.4327</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3663</v>
+        <v>0.0179</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5816</v>
+        <v>0.1497</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7846</v>
+        <v>-0.1319</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5988</v>
+        <v>-2.4718</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1474</v>
+        <v>-3.0472</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5486</v>
+        <v>0.5754</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0072</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0126</v>
+        <v>0.1144</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2842</v>
+        <v>-0.1841</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2716</v>
+        <v>0.2984</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1093</v>
+        <v>-2.8189</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.194</v>
+        <v>-2.0083</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9153</v>
+        <v>-0.8106</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7087</v>
+        <v>-1.8275</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2367</v>
+        <v>-1.8682</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.472</v>
+        <v>0.0407</v>
       </c>
       <c r="J22" t="n">
-        <v>0.247</v>
+        <v>0.3352</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1656</v>
+        <v>-0.2588</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0814</v>
+        <v>0.5941</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9557</v>
+        <v>-2.1627</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4023</v>
+        <v>-1.6093</v>
       </c>
       <c r="O22" t="n">
         <v>-0.5534</v>
       </c>
       <c r="P22" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9796</v>
+        <v>-0.6055</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4759</v>
+        <v>-0.4134</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5037</v>
+        <v>-0.192</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1461</v>
+        <v>-3.1093</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3087</v>
+        <v>-1.194</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8374</v>
+        <v>-1.9153</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8275</v>
+        <v>-1.7087</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8682</v>
+        <v>-1.2367</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0407</v>
+        <v>-0.472</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3352</v>
+        <v>0.247</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2588</v>
+        <v>0.1656</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5941</v>
+        <v>0.0814</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1627</v>
+        <v>-1.9557</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6093</v>
+        <v>-1.4023</v>
       </c>
       <c r="O23" t="n">
         <v>-0.5534</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9326</v>
+        <v>-0.9796</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7139</v>
+        <v>-0.4759</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2188</v>
+        <v>-0.5037</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5667</v>
+        <v>-4.2127</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7507</v>
+        <v>-4.4503</v>
       </c>
       <c r="F24" t="n">
-        <v>0.184</v>
+        <v>0.2375</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4012</v>
@@ -2326,13 +2326,13 @@
         <v>1.9301</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4634</v>
+        <v>-1.1095</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9518</v>
+        <v>-0.6514</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.4581</v>
       </c>
       <c r="V24" t="n">
         <v>1.228</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0274</v>
+        <v>-5.1008</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6727</v>
+        <v>-3.7729</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3547</v>
+        <v>-1.3279</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1005</v>
@@ -2404,13 +2404,13 @@
         <v>2.1231</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0271</v>
+        <v>-0.1005</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1652</v>
+        <v>-0.2654</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1381</v>
+        <v>0.1649</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1278</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-22.737</v>
+        <v>-22.7369</v>
       </c>
       <c r="E26" t="n">
         <v>-16.8596</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.8773</v>
+        <v>-5.8771</v>
       </c>
       <c r="G26" t="n">
         <v>-16.6878</v>
@@ -2452,16 +2452,16 @@
         <v>-13.9208</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.7668</v>
+        <v>-2.766799999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7647000000000004</v>
+        <v>0.7646999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>1.2715</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5067000000000002</v>
+        <v>-0.5066999999999997</v>
       </c>
       <c r="M26" t="n">
         <v>-17.4524</v>
@@ -2485,10 +2485,10 @@
         <v>-6.6826</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.8071</v>
+        <v>-3.807199999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.875599999999999</v>
+        <v>-2.875600000000001</v>
       </c>
       <c r="V26" t="n">
         <v>1.5984</v>
